--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1022,12 +1022,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4572656430</v>
+        <v>4392869596</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1045,19 +1045,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4392869596</v>
+        <v>4572656430</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4384122583</v>
+        <v>4390303473</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1285,19 +1285,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4390303473</v>
+        <v>4384122583</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuild</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1262,12 +1262,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4390303473</v>
+        <v>4384122583</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1285,19 +1285,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4384122583</v>
+        <v>4390303473</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuild</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, гидроплита, сальники | Подходит для DQ200</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1022,12 +1022,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4392869596</v>
+        <v>4572656430</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1045,19 +1045,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4572656430</v>
+        <v>4392869596</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Сепараторная пластина под плиту мехатроника DSG7 прокладки DQ200</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы 0am 0cw dq200 dsg 7</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыльники и сальники W</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Уплотнение резиновое электромотора гидроблока (мехатроника) DQ200 0AM DSG 7</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Прокладка платы электронной мехатроника DSG7 DQ200 0am 0cw</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал Volkswagen Германия</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011Новое поколение (RE0F10A) CVT для Nissan, Mitsubishi, Renault, Jeep</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, Renault, Mitsubishi Новый</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT для Nissan, Renault, Mitsubishi</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW комплект 4 шт (1 половинка)</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Прокладки двигателей</t>
+          <t>Прокладки двигателя</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Корпус фильтра EA888</t>
+          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Фильтры для душа</t>
+          <t>Фильтры для воды в душе</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
+          <t>Обратный клапан масляного фильтра EA888 Gen3 06L115678AD для двигателей 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1022,12 +1022,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4572656430</v>
+        <v>4392869596</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1045,19 +1045,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4392869596</v>
+        <v>4572656430</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -465,8 +465,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>4384124370</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4384124370</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -495,8 +497,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>5882321872</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5882321872</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -525,8 +529,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>4332441059</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4332441059</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,8 +561,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>6244979769</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6244979769</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -585,8 +593,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>5881268930</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5881268930</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -615,8 +625,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>4332439241</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4332439241</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -645,8 +657,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>4332447227</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4332447227</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -675,8 +689,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>4332931669</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4332931669</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -705,8 +721,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>5881268930</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5881268930</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -735,8 +753,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>4332440286</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4332440286</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -765,8 +785,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>6257337024</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6257337024</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -795,8 +817,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>4817587494</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4817587494</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -825,8 +849,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>6250388464</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6250388464</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -855,8 +881,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>5698368883</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5698368883</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -885,8 +913,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>6280776444</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6280776444</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -915,8 +945,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>4387619789</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4387619789</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -945,8 +977,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>4332451430</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4332451430</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -975,8 +1009,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>4333168730</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4333168730</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1005,8 +1041,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>4572654496</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4572654496</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1022,12 +1060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1035,8 +1073,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>4392869596</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4572656430</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1045,19 +1085,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1065,8 +1105,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>4572656430</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4392869596</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1075,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1095,8 +1137,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>4390301546</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4390301546</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1125,8 +1169,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>4332439233</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4332439233</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1155,8 +1201,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>4490648841</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4490648841</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1185,8 +1233,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>4903580771</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4903580771</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1215,8 +1265,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>4483525332</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4483525332</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1245,8 +1297,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>4332495142</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4332495142</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1262,12 +1316,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1275,8 +1329,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>4384122583</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4390303473</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1285,19 +1341,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1305,8 +1361,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>4390303473</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4384122583</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1315,7 +1373,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1335,8 +1393,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>4390304549</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4390304549</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1365,8 +1425,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>6255889487</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6255889487</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1395,8 +1457,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>4332444174</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4332444174</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1425,8 +1489,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>6245087516</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6245087516</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1455,8 +1521,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>4332445106</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4332445106</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1485,8 +1553,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>6244924485</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>6244924485</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1515,8 +1585,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>4384121684</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4384121684</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1545,8 +1617,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>4332446816</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4332446816</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1575,8 +1649,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>4384122529</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4384122529</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1605,8 +1681,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>4332439234</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4332439234</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1635,8 +1713,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>4348864364</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4348864364</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1665,8 +1745,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>4624477268</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4624477268</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1695,8 +1777,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>4332438204</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4332438204</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1725,8 +1809,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>2.26281343670485e+17</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>226281343670484992</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1755,8 +1841,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>4897347756</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4897347756</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1785,8 +1873,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>4332443217</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4332443217</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1815,8 +1905,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>4390304679</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4390304679</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1845,8 +1937,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>5840506209</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5840506209</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1875,8 +1969,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>4461053645</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4461053645</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1905,8 +2001,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>4392843289</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4392843289</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1935,8 +2033,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>5151511654</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5151511654</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1965,8 +2065,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>5151511654</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5151511654</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1995,8 +2097,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>5151511654</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5151511654</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2025,8 +2129,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>4858753907</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4858753907</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2055,8 +2161,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>4858884579</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4858884579</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2085,8 +2193,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>4858815867</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4858815867</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2115,8 +2225,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>4855890143</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4855890143</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2145,8 +2257,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>4872540991</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4872540991</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2175,8 +2289,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>4332438001</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4332438001</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2205,8 +2321,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>4868764206</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4868764206</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2235,8 +2353,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>4868851451</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4868851451</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2265,8 +2385,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>4872038927</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4872038927</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2295,8 +2417,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>4869312987</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4869312987</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2325,8 +2449,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>4872533672</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4872533672</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2355,8 +2481,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>4350106298</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4350106298</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2385,8 +2513,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>6244979944</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>6244979944</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2415,8 +2545,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>4585256166</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4585256166</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2445,8 +2577,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>4375777657</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4375777657</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2475,8 +2609,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>5882321872</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5882321872</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2505,8 +2641,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>5887588650</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5887588650</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2535,8 +2673,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>6250724843</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6250724843</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2565,8 +2705,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>4858671323</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4858671323</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2595,8 +2737,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>4859220987</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4859220987</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2625,8 +2769,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>6244876636</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6244876636</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2655,8 +2801,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>4392848229</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4392848229</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2685,8 +2833,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>4857390773</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4857390773</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2715,8 +2865,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>4855509033</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4855509033</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2745,8 +2897,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>5704416783</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5704416783</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2775,8 +2929,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>2.290505997179453e+17</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>229050599717945344</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2805,8 +2961,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>2.290505966137016e+17</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>229050596613701632</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2835,8 +2993,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>6250724843</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6250724843</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2865,8 +3025,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>6245057523</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6245057523</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2895,8 +3057,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>4461050052</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4461050052</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2925,8 +3089,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>4461049245</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4461049245</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2955,8 +3121,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>6244924495</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6244924495</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2985,8 +3153,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>6250379339</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6250379339</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3015,8 +3185,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>2.290506044278538e+17</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>229050604427853824</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3045,8 +3217,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>6245067593</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>6245067593</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3075,8 +3249,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>6245018050</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>6245018050</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3105,8 +3281,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>2.290505974991299e+17</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>229050597499129856</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3135,8 +3313,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>2.290506007411835e+17</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>229050600741183488</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3165,8 +3345,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>6280776444</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>6280776444</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3195,8 +3377,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>6255889487</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>6255889487</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3225,8 +3409,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>2.262813505575567e+17</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>226281350557556736</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3255,8 +3441,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>6245077872</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>6245077872</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3285,8 +3473,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>6244924346</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>6244924346</t>
+        </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3315,8 +3505,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>6244961358</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>6244961358</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3345,8 +3537,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>2.262813480535081e+17</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>226281348053508096</t>
+        </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3375,8 +3569,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>6244941584</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>6244941584</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3405,8 +3601,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>6250197302</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6250197302</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3435,8 +3633,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>2.26281341770367e+17</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>226281341770366976</t>
+        </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3465,8 +3665,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>6250321939</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>6250321939</t>
+        </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3495,8 +3697,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>6250214306</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>6250214306</t>
+        </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3525,8 +3729,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>6244865322</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>6244865322</t>
+        </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3555,8 +3761,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>6250359522</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>6250359522</t>
+        </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3585,8 +3793,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>6250322137</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>6250322137</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3615,8 +3825,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>2.290506003341189e+17</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>229050600334118912</t>
+        </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3645,8 +3857,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>2.290506041258885e+17</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>229050604125888512</t>
+        </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3675,8 +3889,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>2.290506032243139e+17</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>229050603224313856</t>
+        </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3705,8 +3921,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>2.290506052626104e+17</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>229050605262610432</t>
+        </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3735,8 +3953,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>6245057801</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>6245057801</t>
+        </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3765,8 +3985,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>6250224971</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>6250224971</t>
+        </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3795,8 +4017,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>6244885052</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>6244885052</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3825,8 +4049,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>6257337024</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>6257337024</t>
+        </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3855,8 +4081,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D115" t="n">
-        <v>6245047828</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>6245047828</t>
+        </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3885,8 +4113,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>6250197304</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>6250197304</t>
+        </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3915,8 +4145,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>6245077748</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>6245077748</t>
+        </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3945,8 +4177,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>6244856120</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>6244856120</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3975,8 +4209,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>6244950836</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>6244950836</t>
+        </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4005,8 +4241,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D120" t="n">
-        <v>6244915038</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>6244915038</t>
+        </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4035,8 +4273,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v>6244876340</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>6244876340</t>
+        </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4065,8 +4305,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>6244999088</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>6244999088</t>
+        </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4095,8 +4337,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v>6244884638</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>6244884638</t>
+        </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4125,8 +4369,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D124" t="n">
-        <v>6244941588</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>6244941588</t>
+        </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4155,8 +4401,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D125" t="n">
-        <v>2.290505980903342e+17</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>229050598090334208</t>
+        </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4185,8 +4433,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D126" t="n">
-        <v>2.290505991934566e+17</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>229050599193456640</t>
+        </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4215,8 +4465,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v>2.290506010724884e+17</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>229050601072488448</t>
+        </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4245,8 +4497,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D128" t="n">
-        <v>6245057525</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>6245057525</t>
+        </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4275,8 +4529,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>6220804586</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>6220804586</t>
+        </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4305,8 +4561,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D130" t="n">
-        <v>6245008443</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>6245008443</t>
+        </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4335,8 +4593,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>6244941586</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>6244941586</t>
+        </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4365,8 +4625,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>6245047590</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>6245047590</t>
+        </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4395,8 +4657,10 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>4384120991</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>4384120991</t>
+        </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1316,12 +1316,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4390303473</t>
+          <t>4384122583</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1341,19 +1341,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4384122583</t>
+          <t>4390303473</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Аксессуары для серверов</t>
+          <t>Аксессуары для монтажа серверов</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1316,12 +1316,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4384122583</t>
+          <t>4390303473</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1341,19 +1341,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4390303473</t>
+          <t>4384122583</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1060,12 +1060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4572656430</t>
+          <t>4392869596</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1085,19 +1085,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4392869596</t>
+          <t>4572656430</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1060,12 +1060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4392869596</t>
+          <t>4572656430</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1085,19 +1085,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4572656430</t>
+          <t>4392869596</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4390303473</t>
+          <t>4384122583</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1341,19 +1341,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4384122583</t>
+          <t>4390303473</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1060,12 +1060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4572656430</t>
+          <t>4392869596</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1085,19 +1085,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4392869596</t>
+          <t>4572656430</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4384122583</t>
+          <t>4390303473</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1341,19 +1341,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4390303473</t>
+          <t>4384122583</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1316,12 +1316,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4390303473</t>
+          <t>4384122583</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1341,19 +1341,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4384122583</t>
+          <t>4390303473</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1060,12 +1060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4392869596</t>
+          <t>4572656430</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1085,19 +1085,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4572656430</t>
+          <t>4392869596</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4694,6 +4694,20 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0AM927769F</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0am325025HXF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,12 +900,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025HXF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769F</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6280776444</t>
+          <t>240878387378724864</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0am325025L</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4387619789</t>
+          <t>6280776444</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025L</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4332451430</t>
+          <t>4387619789</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -989,19 +989,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4333168730</t>
+          <t>4332451430</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1028,12 +1028,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4572654496</t>
+          <t>4333168730</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4572656430</t>
+          <t>4572654496</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1085,19 +1085,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4392869596</t>
+          <t>4572656430</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,19 +1117,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4390301546</t>
+          <t>4392869596</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1156,12 +1156,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4332439233</t>
+          <t>4390301546</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1188,12 +1188,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4490648841</t>
+          <t>4332439233</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Сцепление и компоненты</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1220,12 +1220,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4903580771</t>
+          <t>4490648841</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Распределители зажигания автомобильные</t>
+          <t>Сцепление и компоненты</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4483525332</t>
+          <t>4903580771</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Сцепление и компоненты</t>
+          <t>Распределители зажигания автомобильные</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1284,12 +1284,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4332495142</t>
+          <t>4483525332</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Сцепление и компоненты</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1316,12 +1316,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4390303473</t>
+          <t>4332495142</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1348,12 +1348,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4384122583</t>
+          <t>4390303473</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,19 +1373,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4390304549</t>
+          <t>4384122583</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6255889487</t>
+          <t>4390304549</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4332444174</t>
+          <t>6255889487</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1476,12 +1476,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6245087516</t>
+          <t>4332444174</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Прочие запчасти для подвески</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4332445106</t>
+          <t>6245087516</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прочие запчасти для подвески</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6244924485</t>
+          <t>4332445106</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Прочие запчасти для подвески</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1572,12 +1572,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4384121684</t>
+          <t>6244924485</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прочие запчасти для подвески</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1604,12 +1604,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4332446816</t>
+          <t>4384121684</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4384122529</t>
+          <t>4332446816</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1668,12 +1668,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4332439234</t>
+          <t>4384122529</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4348864364</t>
+          <t>4332439234</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Прокладки двигателя</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1732,12 +1732,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4624477268</t>
+          <t>4348864364</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прокладки двигателя</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1764,12 +1764,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4332438204</t>
+          <t>4624477268</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1796,12 +1796,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>226281343670484992</t>
+          <t>4332438204</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1828,12 +1828,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4897347756</t>
+          <t>226281343670484992</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Прочие запчасти для двигателя</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1860,12 +1860,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал VAG 0AM325587E</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4332443217</t>
+          <t>4897347756</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прочие запчасти для двигателя</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1892,12 +1892,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал VAG 0AM325587E</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4390304679</t>
+          <t>4332443217</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5840506209</t>
+          <t>4390304679</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Аксессуары для монтажа серверов</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1956,12 +1956,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0AM927769F</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769F</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4461053645</t>
+          <t>240878386636324864</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Автомобильные бортовые компьютеры</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1988,12 +1988,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов АКПП DSG7 0B5 DL501</t>
+          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2003,29 +2003,29 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4392843289</t>
+          <t>5840506209</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Аксессуары для монтажа серверов</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5151511654</t>
+          <t>4461053645</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2052,12 +2052,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Фильтр-сетка соленоидов АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5151511654</t>
+          <t>4392843289</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2077,19 +2077,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2109,19 +2109,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4858753907</t>
+          <t>5151511654</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Запчасти цилиндро-поршневой группы</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2148,12 +2148,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2163,29 +2163,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4858884579</t>
+          <t>5151511654</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Прочие запчасти для двигателя</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4858815867</t>
+          <t>4858753907</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Двигатели автомобильные</t>
+          <t>Запчасти цилиндро-поршневой группы</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2212,12 +2212,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4855890143</t>
+          <t>4858884579</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Запчасти цилиндро-поршневой группы</t>
+          <t>Прочие запчасти для двигателя</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2244,12 +2244,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4872540991</t>
+          <t>4858815867</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Двигатели автомобильные</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2276,12 +2276,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4332438001</t>
+          <t>4855890143</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Запчасти цилиндро-поршневой группы</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2308,12 +2308,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4868764206</t>
+          <t>4872540991</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2340,12 +2340,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4868851451</t>
+          <t>4332438001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2372,12 +2372,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E Старое поколение RE0F10A CVT для Nissan, Mitsubishi, Renault</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4872038927</t>
+          <t>4868764206</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2397,19 +2397,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4869312987</t>
+          <t>4868851451</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Двигатели автомобильные</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2436,12 +2436,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Гидроблок вариатора JF011E Старое поколение RE0F10A CVT для Nissan, Mitsubishi, Renault</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2451,29 +2451,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4872533672</t>
+          <t>4872038927</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Двигатели автомобильные</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4350106298</t>
+          <t>4869312987</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Автомобильные бортовые компьютеры</t>
+          <t>Двигатели автомобильные</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2500,12 +2500,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6244979944</t>
+          <t>4872533672</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Двигатели автомобильные</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2532,12 +2532,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4585256166</t>
+          <t>4350106298</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Автомобильные бортовые компьютеры</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2564,12 +2564,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4375777657</t>
+          <t>6244979944</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Сцепление и компоненты</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2596,12 +2596,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5882321872</t>
+          <t>4585256166</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2628,12 +2628,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5887588650</t>
+          <t>4375777657</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Запчасти цилиндро-поршневой группы</t>
+          <t>Сцепление и компоненты</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2660,12 +2660,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6250724843</t>
+          <t>5882321872</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4858671323</t>
+          <t>5887588650</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Двигатели автомобильные</t>
+          <t>Запчасти цилиндро-поршневой группы</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2724,12 +2724,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4859220987</t>
+          <t>6250724843</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Прокладки двигателя</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2756,12 +2756,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6244876636</t>
+          <t>4858671323</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Двигатели автомобильные</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2788,12 +2788,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4392848229</t>
+          <t>4859220987</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прокладки двигателя</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2820,12 +2820,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4857390773</t>
+          <t>6244876636</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Фильтры для воды в душе</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2852,12 +2852,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Обратный клапан масляного фильтра EA888 Gen3 06L115678AD для двигателей 1.8 2.0 TSI</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4855509033</t>
+          <t>4392848229</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Масляные фильтры</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2884,12 +2884,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
+          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5704416783</t>
+          <t>4857390773</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Крепления магнитные</t>
+          <t>Фильтры для воды в душе</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2916,12 +2916,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Обратный клапан масляного фильтра EA888 Gen3 06L115678AD для двигателей 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>229050599717945344</t>
+          <t>4855509033</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2948,12 +2948,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>229050596613701632</t>
+          <t>5704416783</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Крепления магнитные</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6250724843</t>
+          <t>229050599717945344</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Масляные фильтры</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6245057523</t>
+          <t>229050596613701632</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Сцепление и компоненты</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4461050052</t>
+          <t>6250724843</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3076,12 +3076,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>jf015</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Комплект подшипников конусов JF015E / RE0F11A, 4 шт оригинал NSK для Nissan, Mitsubishi</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3091,29 +3091,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4461049245</t>
+          <t>6245057523</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Сцепление и компоненты</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6244924495</t>
+          <t>4461050052</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3140,12 +3140,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Комплект подшипников конусов JF015E / RE0F11A, 4 шт оригинал NSK для Nissan, Mitsubishi</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3155,29 +3155,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6250379339</t>
+          <t>4461049245</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Система смазки двигателя</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>229050604427853824</t>
+          <t>6244924495</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3204,12 +3204,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3219,29 +3219,29 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6245067593</t>
+          <t>6250379339</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобильные</t>
+          <t>Система смазки двигателя</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6245018050</t>
+          <t>229050604427853824</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3268,12 +3268,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3283,29 +3283,29 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>229050597499129856</t>
+          <t>6245067593</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Накладки на педали автомобильные</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Пластины на соленоиды мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>229050600741183488</t>
+          <t>6245018050</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,12 +3332,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6280776444</t>
+          <t>229050597499129856</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3364,12 +3364,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Пластины на соленоиды мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6255889487</t>
+          <t>229050600741183488</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3396,12 +3396,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>226281350557556736</t>
+          <t>6280776444</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Масляные фильтры</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3428,12 +3428,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6245077872</t>
+          <t>6255889487</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3460,12 +3460,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6244924346</t>
+          <t>226281350557556736</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Отбойники и пыльники амортизаторов</t>
+          <t>Масляные фильтры</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3492,12 +3492,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6244961358</t>
+          <t>6245077872</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3524,12 +3524,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>226281348053508096</t>
+          <t>6244924346</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Масляные фильтры</t>
+          <t>Отбойники и пыльники амортизаторов</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3556,12 +3556,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6244941584</t>
+          <t>6244961358</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Салонные фильтры</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3588,12 +3588,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6250197302</t>
+          <t>226281348053508096</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Масляные фильтры</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>226281341770366976</t>
+          <t>6244941584</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Салонные фильтры</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6250321939</t>
+          <t>6250197302</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3684,12 +3684,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6250214306</t>
+          <t>226281341770366976</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3716,12 +3716,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3731,12 +3731,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6244865322</t>
+          <t>6250321939</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Сцепление и компоненты</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3748,12 +3748,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6250359522</t>
+          <t>6250214306</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Прочие запчасти для подвески</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3780,12 +3780,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6250322137</t>
+          <t>6244865322</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Прочие запчасти для подвески</t>
+          <t>Сцепление и компоненты</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3812,12 +3812,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>229050600334118912</t>
+          <t>6250359522</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прочие запчасти для подвески</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>229050604125888512</t>
+          <t>6250322137</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прочие запчасти для подвески</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3876,12 +3876,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>229050603224313856</t>
+          <t>229050600334118912</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3908,12 +3908,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>229050605262610432</t>
+          <t>229050604125888512</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3940,12 +3940,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Черное кольцо-прокладка втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6245057801</t>
+          <t>229050603224313856</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Чехлы для рычагов КПП</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3972,12 +3972,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Зеленое кольцо-прокладка втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>6250224971</t>
+          <t>229050605262610432</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4004,12 +4004,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6244885052</t>
+          <t>6245057801</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Прочие запчасти для подвески</t>
+          <t>Чехлы для рычагов КПП</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4036,12 +4036,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6257337024</t>
+          <t>6250224971</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4068,12 +4068,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>6245047828</t>
+          <t>6244885052</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Прочие запчасти для подвески</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4100,12 +4100,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>6250197304</t>
+          <t>6257337024</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6245077748</t>
+          <t>6245047828</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4164,12 +4164,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>6244856120</t>
+          <t>6250197304</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4196,12 +4196,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>6244950836</t>
+          <t>6245077748</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4228,12 +4228,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6244915038</t>
+          <t>6244856120</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4260,12 +4260,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>6244876340</t>
+          <t>6244950836</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Сальники двигателя</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4292,12 +4292,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>6244999088</t>
+          <t>6244915038</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Сальники двигателя</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4324,12 +4324,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6244884638</t>
+          <t>6244876340</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4356,12 +4356,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6244941588</t>
+          <t>6244999088</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Сальники двигателя</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4388,12 +4388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>229050598090334208</t>
+          <t>6244884638</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
+          <t>Сальники двигателя</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4420,12 +4420,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>229050599193456640</t>
+          <t>6244941588</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4452,12 +4452,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>229050601072488448</t>
+          <t>229050598090334208</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4484,12 +4484,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>6245057525</t>
+          <t>229050599193456640</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4516,12 +4516,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6220804586</t>
+          <t>229050601072488448</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Прочие аксессуары для тренажёров</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4548,12 +4548,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>6245008443</t>
+          <t>6245057525</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4580,12 +4580,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>6244941586</t>
+          <t>6220804586</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Аксессуары для велосипедных вилок</t>
+          <t>Прочие аксессуары для тренажёров</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4612,12 +4612,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6245047590</t>
+          <t>6245008443</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Прочие запчасти тормозных систем</t>
+          <t>Запчасти для трансмиссии автомобиля</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4644,30 +4644,94 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>6244941586</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Аксессуары для велосипедных вилок</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>6245047590</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Прочие запчасти тормозных систем</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>0am325025Y</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
         <is>
           <t>4384120991</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Запчасти для трансмиссии автомобиля</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Запчасти для трансмиссии автомобиля</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
@@ -4684,7 +4748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4694,20 +4758,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0AM927769F</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0am325025HXF</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -1092,12 +1092,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4572656430</t>
+          <t>4392869596</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,19 +1117,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4392869596</t>
+          <t>4572656430</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4390303473</t>
+          <t>4384122583</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,19 +1373,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0am325066ac</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Сальник манжет штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4384122583</t>
+          <t>4390303473</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/yandex_market_offers.xlsx
+++ b/data/yandex_market_offers.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: 2 сальника, 2 пыльника, 2 крышки</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1092,12 +1092,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4392869596</t>
+          <t>4572656430</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,19 +1117,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0am325025p</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Клипса штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4572656430</t>
+          <t>4392869596</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Крышка штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Соленоид регулятор давления DSG7 DQ200</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
